--- a/4-2 要件定義/画面要件.xlsx
+++ b/4-2 要件定義/画面要件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\RideTech\自作システム\4-2 要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F5C376-8D5F-46FB-A22B-9A1AEC3A4883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B54F05-001B-4511-ACF6-5D63BCED7E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A9B95F2D-F95B-4AB2-99A6-CCDF7FD4BC40}"/>
   </bookViews>
@@ -288,19 +288,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>案件の詳細表示</t>
-    <rPh sb="0" eb="2">
-      <t>アンケン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>案件詳細</t>
     <rPh sb="0" eb="2">
       <t>アンケン</t>
@@ -650,6 +637,57 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>ヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>案件の詳細表示
+見積実績と配送実績の情報も含めて本画面に統一する
+見積情報は折りたためるようにして必要な情報を見やすくする</t>
+    <rPh sb="0" eb="2">
+      <t>アンケン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ミツモ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ハイソウジッセキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>ホンガメン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>トウイツ</t>
+    </rPh>
+    <rPh sb="33" eb="37">
+      <t>ミツモリジョウホウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ミ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1009,7 +1047,7 @@
   <cols>
     <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="37.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="53.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="54.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="24" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.125" style="1" bestFit="1" customWidth="1"/>
@@ -1018,140 +1056,140 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24">
       <c r="A1" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B1" s="6"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="37.5">
       <c r="A4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="56.25">
       <c r="A5" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="37.5">
       <c r="A6" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="56.25">
       <c r="A9" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="37.5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="75">
       <c r="A11" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>19</v>
